--- a/data/trans_camb/IP11-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP11-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 4,99</t>
+          <t>-5,56; 5,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 4,76</t>
+          <t>-5,87; 5,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 2,28</t>
+          <t>-7,02; 2,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 13,35</t>
+          <t>-0,17; 12,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 2,91</t>
+          <t>-5,73; 2,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 2,32</t>
+          <t>-5,49; 2,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 6,94</t>
+          <t>-1,11; 7,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 2,73</t>
+          <t>-4,43; 2,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 1,16</t>
+          <t>-4,87; 1,34</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-69,49; 182,26</t>
+          <t>-66,52; 199,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-76,19; 156,3</t>
+          <t>-72,68; 199,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-82,66; 94,49</t>
+          <t>-87,37; 124,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 735,33</t>
+          <t>-12,54; 673,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-88,95; 188,77</t>
+          <t>-88,38; 166,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-87,56; 145,11</t>
+          <t>-85,17; 167,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-23,07; 196,66</t>
+          <t>-18,4; 229,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,26; 98,07</t>
+          <t>-67,53; 93,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-75,04; 41,07</t>
+          <t>-72,84; 61,98</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 7,75</t>
+          <t>-4,89; 8,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,24; -0,62</t>
+          <t>-10,25; -0,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 0,6</t>
+          <t>-10,1; 0,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 10,09</t>
+          <t>-2,47; 9,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 3,67</t>
+          <t>-6,9; 3,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 7,54</t>
+          <t>-5,32; 8,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 6,82</t>
+          <t>-1,66; 7,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 0,34</t>
+          <t>-6,77; 0,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 2,6</t>
+          <t>-5,46; 2,67</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-51,97; 228,08</t>
+          <t>-53,66; 193,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 34,98</t>
+          <t>-94,36; 24,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 52,85</t>
+          <t>-100,0; 59,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,37; 265,36</t>
+          <t>-36,53; 254,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,8; 114,11</t>
+          <t>-71,32; 103,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-61,34; 226,87</t>
+          <t>-63,49; 213,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,6; 137,11</t>
+          <t>-21,67; 171,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-75,92; 12,64</t>
+          <t>-74,94; 6,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-64,67; 59,86</t>
+          <t>-65,53; 67,05</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 8,2</t>
+          <t>-5,19; 8,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,61; -0,24</t>
+          <t>-10,2; -0,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 0,54</t>
+          <t>-9,95; 0,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 4,8</t>
+          <t>-7,96; 4,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 5,44</t>
+          <t>-7,79; 5,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 5,32</t>
+          <t>-8,7; 5,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 4,55</t>
+          <t>-4,67; 4,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 1,4</t>
+          <t>-7,37; 1,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 1,43</t>
+          <t>-8,03; 0,94</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-56,81; 315,14</t>
+          <t>-56,31; 336,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; inf</t>
+          <t>-100,0; 129,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 324,16</t>
+          <t>-100,0; 164,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-68,67; 91,22</t>
+          <t>-66,25; 97,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-66,15; 100,69</t>
+          <t>-66,54; 101,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-83,92; 100,85</t>
+          <t>-84,3; 112,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-50,31; 89,33</t>
+          <t>-50,97; 84,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-73,44; 29,73</t>
+          <t>-75,51; 44,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-83,75; 41,8</t>
+          <t>-88,16; 23,61</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 5,36</t>
+          <t>-2,48; 5,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 0,75</t>
+          <t>-6,49; 0,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,47; -0,74</t>
+          <t>-7,72; -0,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 8,87</t>
+          <t>-1,2; 8,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 2,42</t>
+          <t>-5,13; 2,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,56; -0,08</t>
+          <t>-7,49; -0,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 5,51</t>
+          <t>-0,56; 5,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 0,48</t>
+          <t>-4,62; 0,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,31; -1,67</t>
+          <t>-6,46; -1,48</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-36,0; 118,22</t>
+          <t>-32,89; 119,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-72,61; 23,94</t>
+          <t>-71,72; 21,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-86,13; -7,38</t>
+          <t>-85,63; -8,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 161,71</t>
+          <t>-13,5; 161,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-57,42; 50,56</t>
+          <t>-55,78; 68,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-81,17; 4,59</t>
+          <t>-81,18; 8,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 104,23</t>
+          <t>-8,56; 102,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-57,36; 9,55</t>
+          <t>-54,94; 10,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-77,46; -25,39</t>
+          <t>-78,04; -25,37</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,69; 10,39</t>
+          <t>1,46; 10,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 5,98</t>
+          <t>-2,25; 5,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 2,58</t>
+          <t>-4,12; 2,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 6,7</t>
+          <t>-5,39; 6,03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 2,62</t>
+          <t>-7,76; 2,8</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,8; -4,11</t>
+          <t>-12,33; -3,82</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 6,71</t>
+          <t>-0,68; 7,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 2,87</t>
+          <t>-3,84; 3,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,76; -1,96</t>
+          <t>-7,62; -2,03</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>14,6; 1084,25</t>
+          <t>11,95; 1085,88</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-54,12; 719,98</t>
+          <t>-54,85; 618,59</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-86,73; 403,76</t>
+          <t>-90,23; 278,64</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-41,19; 102,91</t>
+          <t>-49,85; 103,44</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-67,22; 53,21</t>
+          <t>-67,36; 58,12</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-97,87; -54,15</t>
+          <t>-97,74; -45,24</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-14,36; 151,84</t>
+          <t>-9,85; 164,37</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-50,42; 66,08</t>
+          <t>-49,94; 75,59</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-90,1; -38,92</t>
+          <t>-90,43; -39,5</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 5,72</t>
+          <t>-5,41; 6,84</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 0,04</t>
+          <t>-7,67; 0,9</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 4,33</t>
+          <t>-5,34; 4,87</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5,29; 18,53</t>
+          <t>4,96; 18,07</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,14; 13,2</t>
+          <t>0,76; 12,89</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 1,42</t>
+          <t>-4,4; 1,21</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,42; 11,26</t>
+          <t>1,91; 10,87</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 5,92</t>
+          <t>-1,57; 5,89</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 2,1</t>
+          <t>-3,4; 1,98</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 617,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1873,37 +1873,37 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t>-86,97; 527,43</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>61,09; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>-23,43; —</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>41,17; —</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>-45,13; —</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26,58; 950,88</t>
+          <t>26,03; 838,67</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-55,6; 517,45</t>
+          <t>-46,45; 399,42</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-83,5; 170,75</t>
+          <t>-82,5; 205,99</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 4,2</t>
+          <t>-0,14; 4,08</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,02; -0,15</t>
+          <t>-3,87; -0,33</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,53; -1,07</t>
+          <t>-4,57; -1,04</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,79</t>
+          <t>0,64; 5,63</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 1,29</t>
+          <t>-2,89; 1,19</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,26; -1,64</t>
+          <t>-5,35; -1,43</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,37</t>
+          <t>1,18; 4,33</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 0,04</t>
+          <t>-2,88; 0,05</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,4; -1,69</t>
+          <t>-4,39; -1,73</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 95,81</t>
+          <t>-3,58; 95,66</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-60,57; -0,85</t>
+          <t>-61,29; -6,49</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-69,71; -22,04</t>
+          <t>-70,71; -19,94</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>17,14; 105,7</t>
+          <t>8,06; 100,82</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-35,87; 24,73</t>
+          <t>-37,35; 24,28</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-69,13; -26,39</t>
+          <t>-69,29; -25,39</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,74; 84,48</t>
+          <t>16,85; 80,4</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-43,01; 0,88</t>
+          <t>-42,16; 1,05</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-64,64; -31,74</t>
+          <t>-65,47; -31,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP11-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP11-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 5,46</t>
+          <t>-5,11; 4,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 5,56</t>
+          <t>-5,31; 5,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 2,46</t>
+          <t>-7,25; 2,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 12,62</t>
+          <t>0,38; 12,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 2,6</t>
+          <t>-5,23; 3,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 2,4</t>
+          <t>-5,98; 2,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 7,08</t>
+          <t>-1,56; 6,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 2,46</t>
+          <t>-4,25; 2,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 1,34</t>
+          <t>-4,99; 1,06</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-66,52; 199,91</t>
+          <t>-65,99; 194,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-72,68; 199,38</t>
+          <t>-69,48; 207,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-87,37; 124,05</t>
+          <t>-85,63; 116,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,54; 673,29</t>
+          <t>-15,93; 605,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-88,38; 166,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,17; 167,25</t>
+          <t>-89,31; 140,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-18,4; 229,31</t>
+          <t>-27,7; 189,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-67,53; 93,85</t>
+          <t>-67,04; 75,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-72,84; 61,98</t>
+          <t>-74,57; 35,33</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 8,0</t>
+          <t>-5,0; 7,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,25; -0,51</t>
+          <t>-10,43; -0,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 0,79</t>
+          <t>-9,97; 0,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 9,97</t>
+          <t>-3,06; 9,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 3,59</t>
+          <t>-7,14; 3,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 8,24</t>
+          <t>-5,07; 8,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 7,32</t>
+          <t>-1,85; 6,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 0,14</t>
+          <t>-7,29; 0,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 2,67</t>
+          <t>-5,79; 3,11</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-53,66; 193,79</t>
+          <t>-52,32; 216,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-94,36; 24,85</t>
+          <t>-94,09; 39,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 59,33</t>
+          <t>-100,0; 54,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-36,53; 254,77</t>
+          <t>-37,5; 267,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-71,32; 103,58</t>
+          <t>-71,42; 112,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-63,49; 213,63</t>
+          <t>-62,1; 230,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,67; 171,88</t>
+          <t>-21,49; 157,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-74,94; 6,54</t>
+          <t>-74,33; 17,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-65,53; 67,05</t>
+          <t>-66,67; 63,64</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 8,09</t>
+          <t>-4,27; 8,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,2; -0,35</t>
+          <t>-9,92; 0,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 0,52</t>
+          <t>-9,58; 0,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 4,61</t>
+          <t>-8,21; 5,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 5,42</t>
+          <t>-7,8; 5,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 5,61</t>
+          <t>-9,13; 5,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 4,23</t>
+          <t>-5,31; 4,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 1,76</t>
+          <t>-7,11; 1,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 0,94</t>
+          <t>-8,09; 1,01</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-56,31; 336,45</t>
+          <t>-57,9; 371,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 129,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 164,94</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-66,25; 97,08</t>
+          <t>-68,62; 106,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-66,54; 101,91</t>
+          <t>-66,53; 133,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-84,3; 112,76</t>
+          <t>-84,44; 133,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-50,97; 84,0</t>
+          <t>-52,56; 87,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-75,51; 44,08</t>
+          <t>-75,44; 35,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-88,16; 23,61</t>
+          <t>-84,49; 32,18</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-3,9</t>
+          <t>-3,89</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 5,56</t>
+          <t>-2,78; 5,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 0,78</t>
+          <t>-6,59; 0,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,72; -0,76</t>
+          <t>-7,51; -0,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 8,16</t>
+          <t>-0,91; 7,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 2,82</t>
+          <t>-5,18; 2,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,49; -0,06</t>
+          <t>-7,74; 0,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 5,5</t>
+          <t>-0,47; 5,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 0,57</t>
+          <t>-4,89; 0,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,46; -1,48</t>
+          <t>-6,41; -1,44</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-61,55%</t>
+          <t>-61,4%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-57,68%</t>
+          <t>-57,6%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,89; 119,2</t>
+          <t>-34,44; 124,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-71,72; 21,44</t>
+          <t>-75,47; 10,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-85,63; -8,59</t>
+          <t>-86,41; -6,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 161,86</t>
+          <t>-12,38; 154,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-55,78; 68,81</t>
+          <t>-55,81; 57,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-81,18; 8,82</t>
+          <t>-81,95; 8,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 102,98</t>
+          <t>-7,63; 113,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-54,94; 10,5</t>
+          <t>-58,59; 13,55</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-78,04; -25,37</t>
+          <t>-77,76; -21,73</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,46; 10,85</t>
+          <t>1,82; 11,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 5,66</t>
+          <t>-1,76; 6,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 2,28</t>
+          <t>-3,91; 2,64</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 6,03</t>
+          <t>-4,95; 7,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 2,8</t>
+          <t>-8,29; 2,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,33; -3,82</t>
+          <t>-12,54; -3,63</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 7,0</t>
+          <t>-0,43; 7,05</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 3,03</t>
+          <t>-4,11; 2,67</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,62; -2,03</t>
+          <t>-7,6; -2,14</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>11,95; 1085,88</t>
+          <t>-1,35; 1178,72</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-54,85; 618,59</t>
+          <t>-50,94; 730,33</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-90,23; 278,64</t>
+          <t>-86,36; 414,16</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-49,85; 103,44</t>
+          <t>-41,34; 119,73</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-67,36; 58,12</t>
+          <t>-68,72; 43,1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-97,74; -45,24</t>
+          <t>-97,1; -44,68</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 164,37</t>
+          <t>-6,92; 158,67</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-49,94; 75,59</t>
+          <t>-50,74; 63,35</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-90,43; -39,5</t>
+          <t>-89,15; -36,76</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 6,84</t>
+          <t>-5,17; 6,04</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 0,9</t>
+          <t>-7,66; 0,47</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 4,87</t>
+          <t>-5,16; 4,54</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4,96; 18,07</t>
+          <t>4,38; 17,98</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,76; 12,89</t>
+          <t>1,14; 13,4</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 1,21</t>
+          <t>-4,96; 1,04</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,91; 10,87</t>
+          <t>2,03; 11,09</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 5,89</t>
+          <t>-1,75; 5,88</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 1,98</t>
+          <t>-3,86; 1,94</t>
         </is>
       </c>
     </row>
@@ -1873,17 +1873,17 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-86,97; 527,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>61,09; —</t>
+          <t>58,58; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-23,43; —</t>
+          <t>-6,17; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26,03; 838,67</t>
+          <t>23,89; 838,03</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-46,45; 399,42</t>
+          <t>-51,08; 449,67</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-82,5; 205,99</t>
+          <t>-87,48; 184,37</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-2,73</t>
+          <t>-2,72</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 4,08</t>
+          <t>-0,05; 4,15</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,87; -0,33</t>
+          <t>-3,8; -0,2</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,57; -1,04</t>
+          <t>-4,54; -0,93</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,63</t>
+          <t>1,03; 5,6</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 1,19</t>
+          <t>-2,99; 1,26</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,35; -1,43</t>
+          <t>-5,2; -1,42</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,33</t>
+          <t>1,06; 4,37</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 0,05</t>
+          <t>-2,83; 0,13</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,39; -1,73</t>
+          <t>-4,45; -1,7</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-51,13%</t>
+          <t>-51,06%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-51,08%</t>
+          <t>-51,05%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 95,66</t>
+          <t>-2,24; 92,3</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-61,29; -6,49</t>
+          <t>-58,81; -4,18</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-70,71; -19,94</t>
+          <t>-70,06; -20,01</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8,06; 100,82</t>
+          <t>12,4; 98,14</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-37,35; 24,28</t>
+          <t>-37,28; 22,89</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-69,29; -25,39</t>
+          <t>-68,17; -23,43</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,85; 80,4</t>
+          <t>15,4; 82,86</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-42,16; 1,05</t>
+          <t>-41,34; 3,33</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-65,47; -31,16</t>
+          <t>-64,72; -31,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP11-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP11-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,88</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,29</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-1,32</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-0,42</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-0,56</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,25</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,88</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,29</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,4</t>
+          <t>-2,23</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,9</t>
+          <t>-1,83</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 4,88</t>
+          <t>0,57; 13,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 5,53</t>
+          <t>-5,72; 2,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 2,56</t>
+          <t>-5,38; 2,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 12,39</t>
+          <t>-5,54; 4,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 3,23</t>
+          <t>-5,95; 4,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 2,28</t>
+          <t>-6,6; 2,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 6,56</t>
+          <t>-1,13; 6,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 2,26</t>
+          <t>-4,14; 2,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 1,06</t>
+          <t>-4,98; 1,27</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>144,93%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-31,77%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-32,57%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-7,42%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-9,9%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-40,1%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>144,93%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-31,77%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-34,57%</t>
+          <t>-39,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-39,09%</t>
+          <t>-37,64%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-65,99; 194,85</t>
+          <t>-7,22; 735,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-69,48; 207,71</t>
+          <t>-88,95; 188,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-85,63; 116,5</t>
+          <t>-86,52; 175,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 605,16</t>
+          <t>-69,49; 182,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-76,19; 156,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-89,31; 140,75</t>
+          <t>-83,05; 95,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,7; 189,54</t>
+          <t>-23,07; 196,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-67,04; 75,27</t>
+          <t>-65,26; 98,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-74,57; 35,33</t>
+          <t>-74,33; 48,21</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,27</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,31</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,8</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,35</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-4,96</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-4,23</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,27</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,31</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>-4,25</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,61</t>
+          <t>-1,79</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 7,64</t>
+          <t>-2,97; 10,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,43; -0,74</t>
+          <t>-7,12; 3,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 0,83</t>
+          <t>-5,53; 7,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 9,95</t>
+          <t>-4,8; 7,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 3,52</t>
+          <t>-10,24; -0,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 8,2</t>
+          <t>-9,52; 0,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 6,75</t>
+          <t>-2,4; 6,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 0,37</t>
+          <t>-6,92; 0,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 3,11</t>
+          <t>-5,72; 2,43</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>49,98%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-20,01%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12,29%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>19,54%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-71,74%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-61,28%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>49,98%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-20,01%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>-61,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-23,88%</t>
+          <t>-26,57%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-52,32; 216,09</t>
+          <t>-32,37; 265,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-94,09; 39,42</t>
+          <t>-76,8; 114,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 54,33</t>
+          <t>-62,95; 217,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,5; 267,37</t>
+          <t>-51,97; 228,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-71,42; 112,88</t>
+          <t>-100,0; 34,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-62,1; 230,25</t>
+          <t>-99,78; 59,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 157,07</t>
+          <t>-28,6; 137,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-74,33; 17,46</t>
+          <t>-75,92; 12,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-66,67; 63,64</t>
+          <t>-66,47; 52,34</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,68</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-1,13</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-2,44</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>1,63</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-4,48</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-4,19</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,68</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-1,13</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,95</t>
+          <t>-4,17</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-3,64</t>
+          <t>-3,52</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 8,28</t>
+          <t>-7,63; 4,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 0,37</t>
+          <t>-7,92; 5,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 0,79</t>
+          <t>-9,0; 6,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 5,35</t>
+          <t>-4,48; 8,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 5,86</t>
+          <t>-10,61; -0,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 5,74</t>
+          <t>-10,07; 0,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 4,48</t>
+          <t>-4,78; 4,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 1,6</t>
+          <t>-7,18; 1,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 1,01</t>
+          <t>-8,01; 1,61</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-19,4%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-13,06%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-28,12%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>29,03%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-79,93%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-74,73%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-19,4%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-13,06%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-33,96%</t>
+          <t>-74,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-48,94%</t>
+          <t>-47,42%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-57,9; 371,61</t>
+          <t>-68,67; 91,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-66,15; 100,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-82,31; 109,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-68,62; 106,71</t>
+          <t>-56,81; 315,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-66,53; 133,19</t>
+          <t>-100,0; inf</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-84,44; 133,28</t>
+          <t>-100,0; 334,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-52,56; 87,84</t>
+          <t>-50,31; 89,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-75,44; 35,2</t>
+          <t>-73,44; 29,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-84,49; 32,18</t>
+          <t>-83,24; 48,6</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,52</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,34</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-4,01</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,37</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-2,71</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,89</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,52</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,34</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,9</t>
+          <t>-3,42</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-3,9</t>
+          <t>-3,71</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 5,5</t>
+          <t>-0,77; 8,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 0,37</t>
+          <t>-5,6; 2,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,51; -0,8</t>
+          <t>-7,66; -0,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 7,94</t>
+          <t>-2,85; 5,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 2,68</t>
+          <t>-6,1; 0,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 0,04</t>
+          <t>-6,79; -0,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 5,8</t>
+          <t>-0,44; 5,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 0,52</t>
+          <t>-4,72; 0,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,41; -1,44</t>
+          <t>-6,14; -1,03</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>48,95%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-18,68%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-55,79%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>21,67%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-42,86%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-61,4%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>48,95%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-18,68%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-54,22%</t>
+          <t>-53,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-57,6%</t>
+          <t>-54,83%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-34,44; 124,93</t>
+          <t>-12,15; 161,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-75,47; 10,6</t>
+          <t>-57,42; 50,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-86,41; -6,28</t>
+          <t>-82,08; 0,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 154,44</t>
+          <t>-36,0; 118,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-55,81; 57,3</t>
+          <t>-72,61; 23,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-81,95; 8,54</t>
+          <t>-81,89; 7,93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 113,52</t>
+          <t>-6,64; 104,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-58,59; 13,55</t>
+          <t>-57,36; 9,55</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-77,76; -21,73</t>
+          <t>-75,16; -16,17</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,81</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-2,62</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-7,59</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>6,15</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2,1</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,5</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,81</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-2,62</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-7,67</t>
+          <t>-0,56</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-4,47</t>
+          <t>-4,43</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,82; 11,23</t>
+          <t>-4,54; 6,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 6,17</t>
+          <t>-7,75; 2,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 2,64</t>
+          <t>-11,69; -3,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 7,22</t>
+          <t>1,69; 10,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 2,55</t>
+          <t>-1,98; 5,98</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,54; -3,63</t>
+          <t>-4,44; 2,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 7,05</t>
+          <t>-1,09; 6,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 2,67</t>
+          <t>-3,91; 2,87</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,6; -2,14</t>
+          <t>-7,68; -1,9</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-29,76%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-86,32%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>224,08%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>76,4%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-18,3%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-29,76%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-87,22%</t>
+          <t>-20,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-73,7%</t>
+          <t>-73,04%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1178,72</t>
+          <t>-41,19; 102,91</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-50,94; 730,33</t>
+          <t>-67,22; 53,21</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-86,36; 414,16</t>
+          <t>-98,06; -48,84</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-41,34; 119,73</t>
+          <t>14,6; 1084,25</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-68,72; 43,1</t>
+          <t>-54,12; 719,98</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-97,1; -44,68</t>
+          <t>-88,22; 390,44</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 158,67</t>
+          <t>-14,36; 151,84</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-50,74; 63,35</t>
+          <t>-50,42; 66,08</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-89,15; -36,76</t>
+          <t>-90,23; -37,22</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>10,76</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>6,06</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-1,04</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-0,0</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-2,86</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-0,35</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>10,76</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>6,06</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-0,95</t>
+          <t>-0,13</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,69</t>
+          <t>-0,58</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 6,04</t>
+          <t>5,29; 18,53</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 0,47</t>
+          <t>1,14; 13,2</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 4,54</t>
+          <t>-5,13; 0,92</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4,38; 17,98</t>
+          <t>-4,75; 5,72</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,14; 13,4</t>
+          <t>-7,66; 0,04</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 1,04</t>
+          <t>-5,29; 4,8</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,03; 11,09</t>
+          <t>1,42; 11,26</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 5,88</t>
+          <t>-2,02; 5,92</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 1,94</t>
+          <t>-3,47; 2,36</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>629,64%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>354,91%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-60,98%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-0,1%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-75,29%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-9,11%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>629,64%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>354,91%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-55,36%</t>
+          <t>-3,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-25,03%</t>
+          <t>-21,0%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>41,17; —</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>-45,13; —</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 617,71</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>58,58; —</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>-6,17; —</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23,89; 838,03</t>
+          <t>26,58; 950,88</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-51,08; 449,67</t>
+          <t>-55,6; 517,45</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-87,48; 184,37</t>
+          <t>-82,09; 198,24</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>3,41</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,85</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-3,36</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>2,0</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-2,03</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-2,72</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>3,41</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-0,85</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-3,38</t>
+          <t>-2,57</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-3,06</t>
+          <t>-2,98</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 4,15</t>
+          <t>1,32; 5,79</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,8; -0,2</t>
+          <t>-2,78; 1,29</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,54; -0,93</t>
+          <t>-5,29; -1,57</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,6</t>
+          <t>-0,16; 4,2</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 1,26</t>
+          <t>-4,02; -0,15</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,2; -1,42</t>
+          <t>-4,41; -0,81</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,37</t>
+          <t>0,98; 4,37</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 0,13</t>
+          <t>-2,87; 0,04</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,45; -1,7</t>
+          <t>-4,24; -1,67</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>51,65%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-12,86%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-51,0%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>37,55%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-38,04%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-51,06%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>51,65%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-12,86%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-51,31%</t>
+          <t>-48,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-51,05%</t>
+          <t>-49,68%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 92,3</t>
+          <t>17,14; 105,7</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-58,81; -4,18</t>
+          <t>-35,87; 24,73</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-70,06; -20,01</t>
+          <t>-69,39; -25,4</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12,4; 98,14</t>
+          <t>-4,06; 95,81</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-37,28; 22,89</t>
+          <t>-60,57; -0,85</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-68,17; -23,43</t>
+          <t>-68,8; -17,1</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,4; 82,86</t>
+          <t>14,74; 84,48</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-41,34; 3,33</t>
+          <t>-43,01; 0,88</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-64,72; -31,75</t>
+          <t>-63,68; -30,46</t>
         </is>
       </c>
     </row>
